--- a/output/pdf_financials_xlsx/AAA.P.xlsx
+++ b/output/pdf_financials_xlsx/AAA.P.xlsx
@@ -479,25 +479,17 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -506,25 +498,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -533,25 +517,17 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -560,25 +536,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>7.8e-05</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.000782</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.000906</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.001004</v>
       </c>
     </row>
     <row r="8">
@@ -587,25 +555,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -614,25 +574,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -641,25 +593,17 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>7.8e-05</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.000782</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.000906</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.001004</v>
       </c>
     </row>
     <row r="11">
@@ -668,25 +612,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-7.8e-05</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.000782</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.000906</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.001004</v>
       </c>
     </row>
     <row r="12">
@@ -695,25 +631,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -722,25 +650,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -749,25 +669,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -776,25 +688,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -803,25 +707,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.005134</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.098609</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="17">
@@ -830,25 +726,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -911,25 +799,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.005134</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.098609</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="21">
@@ -938,25 +818,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -965,25 +837,17 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1030,25 +894,17 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -1062,10 +918,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>4.93045</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1084,25 +938,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.005134</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.098609</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="28">
@@ -1111,25 +957,17 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1138,25 +976,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.005134</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.098609</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="30">
@@ -1192,25 +1022,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1253,25 +1075,17 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1280,25 +1094,17 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1307,25 +1113,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1334,25 +1132,17 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1361,25 +1151,17 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1388,25 +1170,17 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1415,25 +1189,17 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1442,25 +1208,17 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1469,25 +1227,17 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1496,25 +1246,17 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1523,25 +1265,17 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1550,25 +1284,17 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1577,25 +1303,17 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1604,25 +1322,17 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1631,25 +1341,17 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.194922</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.454283</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.454283</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1658,20 +1360,14 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.194922</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.454283</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.454283</v>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
@@ -1685,25 +1381,17 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1712,25 +1400,17 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1739,25 +1419,17 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1766,25 +1438,17 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1793,25 +1457,17 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1847,25 +1503,17 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1874,25 +1522,17 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1901,25 +1541,17 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1928,25 +1560,17 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1955,25 +1579,17 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1982,25 +1598,17 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2009,20 +1617,14 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>-0.07685</v>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
@@ -2055,25 +1657,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2082,25 +1676,17 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2109,25 +1695,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2136,25 +1714,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2182,25 +1752,17 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2209,25 +1771,17 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2236,25 +1790,17 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2263,25 +1809,17 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2290,25 +1828,17 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2317,25 +1847,17 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2344,25 +1866,17 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2398,25 +1912,17 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2425,25 +1931,17 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2452,25 +1950,17 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2506,25 +1996,17 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2533,25 +2015,17 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2560,25 +2034,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2587,25 +2053,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2614,25 +2072,17 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2687,25 +2137,17 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.487529</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.487529</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.487529</v>
       </c>
     </row>
     <row r="89">
@@ -2714,25 +2156,17 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2760,25 +2194,17 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2787,25 +2213,17 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2814,25 +2232,17 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2860,25 +2270,17 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2887,25 +2289,17 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.189866</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.415286</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.309317</v>
       </c>
     </row>
     <row r="97">
@@ -2940,25 +2334,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.005134</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.098609</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="100">
@@ -2967,25 +2353,17 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2994,25 +2372,17 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3021,25 +2391,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3048,25 +2410,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.00546</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3094,25 +2448,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3121,25 +2467,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.005056</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.028481</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.014534</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.003691</v>
       </c>
     </row>
     <row r="107">
@@ -3148,23 +2486,17 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.0148</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3173,25 +2505,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3200,25 +2524,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3227,25 +2543,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3254,25 +2562,17 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3281,25 +2581,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3308,25 +2600,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3335,25 +2619,17 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3362,25 +2638,17 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3389,25 +2657,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3416,25 +2676,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3443,25 +2695,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3470,15 +2714,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -3497,25 +2737,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3524,25 +2756,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3551,25 +2775,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3578,25 +2794,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3605,25 +2813,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3632,25 +2832,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3659,25 +2851,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3713,25 +2897,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.095771</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3763,10 +2939,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.194922</v>
@@ -3784,25 +2958,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3811,25 +2977,17 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.194922</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.253901</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.07139</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.052804</v>
       </c>
     </row>
     <row r="133">
@@ -3857,25 +3015,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3884,25 +3034,17 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-7.8e-05</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.055328</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.07139</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.052804</v>
       </c>
     </row>
   </sheetData>
@@ -3916,7 +3058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4356,19 +3498,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>377,433</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current assets total</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.194922</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.454283</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.454283</v>
@@ -4762,35 +3904,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Current assets total</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Loss for the period</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>0.194922</v>
+        <v>-0.005134</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.454283</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.098609</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="25">
@@ -4806,21 +3948,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loss for the period</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>-0.005134</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>-0.098609</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-0.056856</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-0.049113</v>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -4831,17 +3985,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Prepaid expense</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4849,15 +4003,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>-0.00546</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.00546</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4878,25 +4028,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prepaid expense</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.005056</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.00546</v>
+        <v>0.033941</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.00546</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019994</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>-0.003691</v>
       </c>
     </row>
     <row r="28">
@@ -4912,25 +4062,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.005056</v>
+        <v>-7.8e-05</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.033941</v>
+        <v>-0.055328</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.019994</v>
+        <v>-0.07139</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-0.003691</v>
+        <v>-0.052804</v>
       </c>
     </row>
     <row r="29">
@@ -4946,19 +4096,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Change in cash, for the period</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>-7.8e-05</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>-0.055328</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G29" s="5" t="n">
         <v>-0.07139</v>
@@ -4980,10 +4134,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Change in cash, for the period</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Cash - beginning of the period</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4995,10 +4153,10 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.07139</v>
+        <v>0.448823</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-0.052804</v>
+        <v>0.377433</v>
       </c>
     </row>
     <row r="31">
@@ -5014,12 +4172,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash - beginning of the period</t>
+          <t>Cash - end of the period</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5033,10 +4191,10 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.448823</v>
+        <v>0.377433</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.377433</v>
+        <v>0.324629</v>
       </c>
     </row>
     <row r="32">
@@ -5047,17 +4205,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash - end of the period</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5065,16 +4223,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.377433</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.324629</v>
+      <c r="F32" s="5" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -5085,26 +4245,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Proceeds from issuance of shares (Note</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.195</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.0148</v>
+        <v>5e-06</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5130,19 +4288,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares (Note</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0.195</v>
+          <t>Proceeds from Initial Public Offering</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5168,17 +4324,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Proceeds from Initial Public Offering</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Finder’s fees and share issuance costs</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.4</v>
+        <v>-0.095771</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5204,17 +4364,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finder’s fees and share issuance costs</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Proceeds from issuance of shares (Note 5)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.095771</v>
+        <v>0.005</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5240,21 +4404,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares (Note 5)</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.195</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.005</v>
+        <v>0.309229</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5280,19 +4442,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Change in cash, for the period</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.195</v>
+        <v>0.194922</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.309229</v>
+        <v>0.253901</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5318,15 +4480,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Change in cash, for the period</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
+          <t>Cash - beginning of period</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
         <v>0.194922</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.253901</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5352,21 +4520,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash - beginning of period</t>
+          <t>Cash - end of period</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.194922</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.194922</v>
+        <v>0.448823</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5382,39 +4548,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash - end of period</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.194922</v>
+        <v>7.8e-05</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.448823</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000782</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.000906</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.001004</v>
       </c>
     </row>
     <row r="42">
@@ -5430,21 +4592,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Regulatory and filing fees</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>7.8e-05</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.000782</v>
+        <v>0.034357</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.000906</v>
+        <v>0.019186</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.001004</v>
+        <v>0.030482</v>
       </c>
     </row>
     <row r="43">
@@ -5460,23 +4624,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.004573</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.034357</v>
+        <v>0.048658</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.019186</v>
+        <v>0.036764</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.030482</v>
+        <v>0.017627</v>
       </c>
     </row>
     <row r="44">
@@ -5492,25 +4658,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Loss and comprehensive loss for the period</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.004573</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.048658</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.036764</v>
+        <v>-0.056856</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.017627</v>
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="45">
@@ -5521,34 +4691,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.056856</v>
+        <v>-1e-08</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>-0.049113</v>
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="46">
@@ -5559,30 +4725,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>-2e-08</v>
+          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-1e-08</v>
+        <v>8</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-1e-08</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -5593,30 +4759,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>From February 3,</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
+          <t>2022 February</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>8</v>
+      <c r="E47" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>2.8e-05</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -5627,20 +4793,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>From February 3,</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2022 February</t>
+          <t>Office and admins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.000483</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>1.2e-05</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5661,20 +4827,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Stock-based compensation 14,800</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Office and admins</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
-        <v>0.000483</v>
+        <v>-0.005134</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1.2e-05</v>
+        <v>-0.098609</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5695,24 +4865,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stock-based compensation 14,800</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period</t>
+          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.005134</v>
+        <v>2.608</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.098609</v>
+        <v>6.03726</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5720,44 +4890,6 @@
         </is>
       </c>
       <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>2.608</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>6.03726</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/AAA.P.xlsx
+++ b/output/pdf_financials_xlsx/AAA.P.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/AAA.P.xlsx
+++ b/output/pdf_financials_xlsx/AAA.P.xlsx
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1355,7 +1355,7 @@
         <v>0.454283</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.454283</v>
+        <v>0.377433</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0.454283</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.454283</v>
+        <v>0.377433</v>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>-0.07685</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cash 377,433</t>
+          <t>Prepaid assets</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3438,13 +3438,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.448823</v>
+      <c r="F11" s="5" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -3465,26 +3465,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prepaid assets -</t>
+          <t>Current assets total</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.194922</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.454283</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.00546</v>
+        <v>0.377433</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3495,58 +3491,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Current assets total</t>
+          <t>Loss for the period</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.194922</v>
+        <v>-0.005134</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.454283</v>
+        <v>-0.098609</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.454283</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.056856</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total assets 377,433</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3559,8 +3553,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>0.454283</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3571,18 +3567,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 8) 19,003</t>
+          <t>Prepaid expense</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3590,13 +3590,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="5" t="n">
+        <v>-0.00546</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.038997</v>
+        <v>0.00546</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3607,96 +3605,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total liabilities 19,003</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.005056</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.033941</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.038997</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019994</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.003691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Share capital (Note 5) 487,529</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.8e-05</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.055328</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.487529</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.07139</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.052804</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Reserves (Note 5) 31,500</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Change in cash, for the period</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3708,31 +3702,33 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.07139</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.052804</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deficit (160,599)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Cash - beginning of the period</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3744,33 +3740,31 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.103743</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.448823</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.377433</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity 358,430</t>
+          <t>Cash - end of the period</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3784,33 +3778,31 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.415286</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.377433</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.324629</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity 377,433</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3818,13 +3810,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="5" t="n">
+        <v>-0.098609</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.454283</v>
+        <v>-0.056856</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3835,32 +3825,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nature of operations and going concern -Note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>1e-06</v>
+      <c r="F22" s="5" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3871,31 +3865,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prepaid assets</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
+          <t>Proceeds from Initial Public Offering</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.00546</v>
+        <v>0.4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3916,30 +3906,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loss for the period</t>
+          <t>Finder’s fees and share issuance costs</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>-0.005134</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.098609</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-0.056856</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>-0.049113</v>
+        <v>-0.095771</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -3950,17 +3946,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Proceeds from issuance of shares (Note 5)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3968,10 +3964,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3992,29 +3986,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prepaid expense</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.195</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.00546</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.00546</v>
+        <v>0.309229</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4030,30 +4024,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Change in cash, for the year</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.005056</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.033941</v>
+        <v>0.253901</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.019994</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-0.003691</v>
+        <v>-0.07139</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -4064,30 +4062,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Cash - beginning of year</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>-7.8e-05</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.055328</v>
+        <v>0.194922</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.07139</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-0.052804</v>
+        <v>0.448823</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -4098,17 +4100,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Change in cash, for the period</t>
+          <t>Cash - end of year</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4116,16 +4118,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="5" t="n">
+        <v>0.448823</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.07139</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>-0.052804</v>
+        <v>0.377433</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -4136,34 +4138,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash - beginning of the period</t>
+          <t>Proceeds from issuance of shares (Note</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.448823</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.377433</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -4174,34 +4176,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash - end of the period</t>
+          <t>Change in cash, for the period</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.377433</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>0.324629</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.194922</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.253901</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -4212,17 +4214,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Cash - beginning of period</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4231,7 +4233,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.194922</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4257,19 +4259,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares (Note</t>
+          <t>Cash - end of period</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.195</v>
+        <v>0.194922</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.448823</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4285,261 +4287,229 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds from Initial Public Offering</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>7.8e-05</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000782</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.000906</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.001004</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finder’s fees and share issuance costs</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Regulatory and filing fees</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.095771</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.034357</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.019186</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.030482</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares (Note 5)</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.004573</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.048658</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.036764</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.017627</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Loss and comprehensive loss for the period</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>0.309229</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.056856</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>-0.049113</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Change in cash, for the period</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.194922</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.253901</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash - beginning of period</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.194922</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.03726</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash - end of period</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Office and admins</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>0.194922</v>
+        <v>0.000483</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.448823</v>
+        <v>1.2e-05</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4565,25 +4535,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>7.8e-05</v>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.000782</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.000906</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.001004</v>
+        <v>0.0148</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -4599,23 +4571,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.034357</v>
+        <v>-0.098609</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.019186</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>0.030482</v>
+        <v>-0.056856</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -4626,30 +4604,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>From February 3,</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>2022 February</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.004573</v>
+        <v>0.002021</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.048658</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.036764</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>0.017627</v>
+        <v>2.8e-05</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -4660,7 +4638,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Stock-based compensation                                                                    14,800</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4673,21 +4651,21 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.056856</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>-0.049113</v>
+      <c r="E44" s="5" t="n">
+        <v>-0.005134</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>-0.098609</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -4703,7 +4681,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4712,191 +4690,17 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>2.608</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>From February 3,</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2022 February</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Office and admins</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>0.000483</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Stock-based compensation 14,800</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Loss and comprehensive loss for the period</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>-0.005134</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-0.098609</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding (basic and diluted)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>2.608</v>
-      </c>
-      <c r="F50" s="5" t="n">
         <v>6.03726</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/AAA.P.xlsx
+++ b/output/pdf_financials_xlsx/AAA.P.xlsx
@@ -2224,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0315</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0315</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="93">
@@ -3294,7 +3294,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AAA.P.xlsx
+++ b/output/pdf_financials_xlsx/AAA.P.xlsx
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.194922</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.448823</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.377433</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.324629</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.194922</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.448823</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.377433</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.324629</v>
       </c>
     </row>
     <row r="37">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.194922</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.454283</v>
+        <v>0.00546</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.377433</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
